--- a/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
+++ b/PCB Lattice/V3/BOM PPU_LITE_LATT_V3.xlsx
@@ -5024,7 +5024,7 @@
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
       <c r="D22" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>91</v>
@@ -5178,7 +5178,7 @@
         <v>19</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>41</v>
